--- a/Result/profitability/2357.xlsx
+++ b/Result/profitability/2357.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.92</v>
       </c>
       <c r="M2" t="n">
-        <v>11.7675</v>
+        <v>12.86875</v>
       </c>
       <c r="N2" t="n">
-        <v>15.25625</v>
+        <v>15.16</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.6</v>
       </c>
       <c r="M3" t="n">
-        <v>9.86375</v>
+        <v>12.7925</v>
       </c>
       <c r="N3" t="n">
-        <v>14.485</v>
+        <v>14.51625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.54</v>
       </c>
       <c r="M4" t="n">
-        <v>9.779999999999999</v>
+        <v>10.8325</v>
       </c>
       <c r="N4" t="n">
-        <v>13.9</v>
+        <v>13.96375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.76</v>
       </c>
       <c r="M5" t="n">
-        <v>7.532500000000001</v>
+        <v>9.0875</v>
       </c>
       <c r="N5" t="n">
-        <v>12.835</v>
+        <v>13.255</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.11</v>
       </c>
       <c r="M6" t="n">
-        <v>5.89625</v>
+        <v>7.324999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>12.10125</v>
+        <v>12.45625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>4.11625</v>
+        <v>5.40125</v>
       </c>
       <c r="N7" t="n">
-        <v>11.64125</v>
+        <v>11.795</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.53</v>
       </c>
       <c r="M8" t="n">
-        <v>2.3875</v>
+        <v>3.94375</v>
       </c>
       <c r="N8" t="n">
-        <v>11.2025</v>
+        <v>11.49125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>257732</v>
+      </c>
+      <c r="D75" t="n">
+        <v>213488</v>
+      </c>
+      <c r="E75" t="n">
+        <v>44244</v>
+      </c>
+      <c r="F75" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="G75" t="n">
+        <v>20974</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.14%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>5283</v>
+      </c>
+      <c r="J75" t="n">
+        <v>26257</v>
+      </c>
+      <c r="K75" t="n">
+        <v>19048</v>
+      </c>
+      <c r="L75" t="n">
+        <v>25.64</v>
+      </c>
+      <c r="M75" t="n">
+        <v>14.7325</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.95375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.9438968915845338</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.310000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1554508748317633</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.9424242424242426</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.360000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2433019551049964</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
